--- a/data_management2026/to_be_interpretation.xlsx
+++ b/data_management2026/to_be_interpretation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tippi\SynologyDrive\Tsing_Hua\third_grade\project\RealTimeAccompaniment_COPY\data_management2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74550A24-0D4D-4A1C-AB63-E015CC28F072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCBF4426-28A2-417D-B764-B063CE72599E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{70DF922D-9D6F-4B38-87EE-D8EAAE945BEC}"/>
   </bookViews>
@@ -39,11 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="24">
-  <si>
-    <t>202412 Experiments\20241217\Recordings Edit 2.tracktionedit</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
   <si>
     <t>202412 Experiments\20241217\Recordings Edit 3.tracktionedit</t>
   </si>
@@ -125,13 +121,6 @@
     <t>data_management2026/202412 Experiments/20241218/inputmslog_Take_3_Human_2.txt</t>
   </si>
   <si>
-    <t>data_management2026/202412 Experiments/20241218/inputmslog_Take_5_Human_1.txt</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>data_management2026/202412 Experiments/20241218/inputmslog_Take_5_Human_2.txt</t>
-  </si>
-  <si>
     <t>Debussy 4</t>
   </si>
   <si>
@@ -141,9 +130,6 @@
   <si>
     <t>data_management2026/202412 Experiments/20241218/inputmslog_Take_4_Human_1.txt</t>
     <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>faure 1</t>
   </si>
   <si>
     <t>faure 1</t>
@@ -578,34 +564,34 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.5">
@@ -614,20 +600,20 @@
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2" s="5">
         <v>45644</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="1"/>
@@ -638,20 +624,20 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3" s="5">
         <v>45644</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="1"/>
@@ -662,20 +648,20 @@
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4" s="5">
         <v>45644</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="1">
@@ -688,20 +674,20 @@
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5" s="5">
         <v>45644</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="1">
@@ -714,14 +700,14 @@
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="E6" s="4"/>
       <c r="F6" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6" s="5">
         <v>45644</v>
@@ -730,59 +716,23 @@
         <v>0</v>
       </c>
       <c r="I6" s="3"/>
-      <c r="J6" s="1">
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="16.5" x14ac:dyDescent="0.5">
-      <c r="A7" s="1">
-        <v>1006</v>
-      </c>
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A7" s="1"/>
       <c r="B7" s="3"/>
-      <c r="C7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
       <c r="E7" s="3"/>
-      <c r="F7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="5">
-        <v>45644</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>0</v>
-      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="3"/>
       <c r="I7" s="3"/>
-      <c r="J7" s="1">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="16.5" x14ac:dyDescent="0.5">
-      <c r="A8" s="1">
-        <v>1007</v>
-      </c>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="A8" s="1"/>
       <c r="B8" s="3"/>
-      <c r="C8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="5">
-        <v>45644</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" s="3"/>
-      <c r="J8" s="1"/>
     </row>
     <row r="9" spans="1:10" ht="16.5" x14ac:dyDescent="0.5">
       <c r="A9" s="1"/>
